--- a/process/configuration/templates/_report_configuration.xlsx
+++ b/process/configuration/templates/_report_configuration.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rmiteduau-my.sharepoint.com/personal/carl_higgs_rmit_edu_au/Documents/projects/global-indicators/process/configuration/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rmiteduau-my.sharepoint.com/personal/carl_higgs_rmit_edu_au/Documents/projects/global-indicators/process/configuration/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="363" documentId="13_ncr:1_{974DC119-FBC5-4146-98A2-4FA425A99853}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F80D3D92-49EA-4625-9A3C-0DA31462B0D4}"/>
+  <xr:revisionPtr revIDLastSave="368" documentId="13_ncr:1_{974DC119-FBC5-4146-98A2-4FA425A99853}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B858FA20-6F52-457E-A945-5BA9DEBB829C}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="policy_spatial" sheetId="1" r:id="rId1"/>
@@ -16593,7 +16593,14 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="4">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -16608,20 +16615,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
     </dxf>
@@ -19237,8 +19230,8 @@
         <v>14</v>
       </c>
       <c r="E39">
-        <f>G38+20</f>
-        <v>126</v>
+        <f>G38+26</f>
+        <v>132</v>
       </c>
       <c r="F39">
         <f t="shared" si="7"/>
@@ -19246,7 +19239,7 @@
       </c>
       <c r="G39">
         <f t="shared" si="8"/>
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="H39" t="s">
         <v>102</v>
@@ -19298,7 +19291,7 @@
       </c>
       <c r="E40">
         <f>G39+4</f>
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="F40">
         <f t="shared" si="7"/>
@@ -19306,7 +19299,7 @@
       </c>
       <c r="G40">
         <f t="shared" si="8"/>
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="H40" t="s">
         <v>102</v>
@@ -19358,7 +19351,7 @@
       </c>
       <c r="E41">
         <f>G40+12</f>
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="F41">
         <f t="shared" si="7"/>
@@ -19366,7 +19359,7 @@
       </c>
       <c r="G41">
         <f t="shared" si="8"/>
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="H41" t="s">
         <v>102</v>
@@ -19418,7 +19411,7 @@
       </c>
       <c r="E42">
         <f>G41+4</f>
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="F42">
         <f t="shared" si="7"/>
@@ -19426,7 +19419,7 @@
       </c>
       <c r="G42">
         <f t="shared" si="8"/>
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="H42" t="s">
         <v>102</v>
@@ -19478,7 +19471,7 @@
       </c>
       <c r="E43">
         <f>G42+28</f>
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="F43">
         <f t="shared" si="7"/>
@@ -19486,7 +19479,7 @@
       </c>
       <c r="G43">
         <f t="shared" si="8"/>
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="H43" t="s">
         <v>102</v>
@@ -19538,7 +19531,7 @@
       </c>
       <c r="E44">
         <f>G43+4</f>
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="F44">
         <f t="shared" si="7"/>
@@ -19546,7 +19539,7 @@
       </c>
       <c r="G44">
         <f t="shared" si="8"/>
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="H44" t="s">
         <v>102</v>
@@ -38988,15 +38981,15 @@
         <v>14</v>
       </c>
       <c r="E40">
-        <f>G39+20</f>
-        <v>114</v>
+        <f>G39+26</f>
+        <v>120</v>
       </c>
       <c r="F40">
         <v>196</v>
       </c>
       <c r="G40">
         <f t="shared" si="6"/>
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="H40" t="s">
         <v>102</v>
@@ -39047,14 +39040,14 @@
       </c>
       <c r="E41">
         <f>G40+4</f>
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="F41">
         <v>196</v>
       </c>
       <c r="G41">
         <f t="shared" si="6"/>
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="H41" t="s">
         <v>102</v>
@@ -39105,14 +39098,14 @@
       </c>
       <c r="E42">
         <f>G41+26</f>
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="F42">
         <v>196</v>
       </c>
       <c r="G42">
         <f t="shared" si="6"/>
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="H42" t="s">
         <v>102</v>
@@ -39163,14 +39156,14 @@
       </c>
       <c r="E43">
         <f>G42+4</f>
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="F43">
         <v>196</v>
       </c>
       <c r="G43">
         <f t="shared" si="6"/>
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="H43" t="s">
         <v>102</v>
@@ -39221,14 +39214,14 @@
       </c>
       <c r="E44">
         <f>G43+16</f>
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="F44">
         <v>196</v>
       </c>
       <c r="G44">
         <f t="shared" si="6"/>
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="H44" t="s">
         <v>102</v>
@@ -39279,14 +39272,14 @@
       </c>
       <c r="E45">
         <f>G44+4</f>
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="F45">
         <v>196</v>
       </c>
       <c r="G45">
         <f t="shared" si="6"/>
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="H45" t="s">
         <v>102</v>
@@ -46092,15 +46085,15 @@
         <v>14</v>
       </c>
       <c r="E39">
-        <f>G38+20</f>
-        <v>115</v>
+        <f>G38+26</f>
+        <v>121</v>
       </c>
       <c r="F39">
         <v>196</v>
       </c>
       <c r="G39">
         <f t="shared" si="6"/>
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="H39" t="s">
         <v>102</v>
@@ -46151,14 +46144,14 @@
       </c>
       <c r="E40">
         <f>G39+4</f>
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="F40">
         <v>196</v>
       </c>
       <c r="G40">
         <f t="shared" si="6"/>
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="H40" t="s">
         <v>102</v>
@@ -46209,14 +46202,14 @@
       </c>
       <c r="E41">
         <f>G40+12</f>
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="F41">
         <v>196</v>
       </c>
       <c r="G41">
         <f t="shared" si="6"/>
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="H41" t="s">
         <v>102</v>
@@ -46267,14 +46260,14 @@
       </c>
       <c r="E42">
         <f>G41+4</f>
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="F42">
         <v>196</v>
       </c>
       <c r="G42">
         <f t="shared" si="6"/>
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="H42" t="s">
         <v>102</v>
@@ -46325,14 +46318,14 @@
       </c>
       <c r="E43">
         <f>G42+28</f>
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="F43">
         <v>196</v>
       </c>
       <c r="G43">
         <f t="shared" si="6"/>
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="H43" t="s">
         <v>102</v>
@@ -46383,14 +46376,14 @@
       </c>
       <c r="E44">
         <f>G43+4</f>
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="F44">
         <v>196</v>
       </c>
       <c r="G44">
         <f t="shared" si="6"/>
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="H44" t="s">
         <v>102</v>
@@ -77391,19 +77384,14 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:B150 B162:B1048576">
-    <cfRule type="duplicateValues" dxfId="4" priority="111"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C1:BB150 C162:BB179">
-    <cfRule type="containsBlanks" dxfId="3" priority="73">
-      <formula>LEN(TRIM(C1))=0</formula>
-    </cfRule>
+    <cfRule type="duplicateValues" dxfId="3" priority="111"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B151:B161">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C151:BB161">
-    <cfRule type="containsBlanks" dxfId="0" priority="1">
-      <formula>LEN(TRIM(C151))=0</formula>
+  <conditionalFormatting sqref="C1:BB179">
+    <cfRule type="containsBlanks" dxfId="1" priority="1">
+      <formula>LEN(TRIM(C1))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -78340,7 +78328,7 @@
     <mergeCell ref="A2:A3"/>
   </mergeCells>
   <conditionalFormatting sqref="A5:A20">
-    <cfRule type="containsBlanks" dxfId="2" priority="1">
+    <cfRule type="containsBlanks" dxfId="0" priority="1">
       <formula>LEN(TRIM(A5))=0</formula>
     </cfRule>
   </conditionalFormatting>

--- a/process/configuration/templates/_report_configuration.xlsx
+++ b/process/configuration/templates/_report_configuration.xlsx
@@ -78941,6 +78941,233 @@
 </worksheet>
 </file>
 
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E46915CC77A6414794C0659BE0416FBE" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ce73daeef664d7c8d016e21b47135507">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="d026c80c-8c89-4d76-b5a4-adafffa27ea9" xmlns:ns3="0f2f1471-5c80-47c6-b5fc-5f7f410df7a8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="6117017243beacc659db0547db5dd191" ns2:_="" ns3:_="">
+    <xsd:import namespace="d026c80c-8c89-4d76-b5a4-adafffa27ea9"/>
+    <xsd:import namespace="0f2f1471-5c80-47c6-b5fc-5f7f410df7a8"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="d026c80c-8c89-4d76-b5a4-adafffa27ea9" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="12" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="13" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="14" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="16" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="c921d02d-b337-4ce5-bd1c-22d9132a6b17" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="18" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="0f2f1471-5c80-47c6-b5fc-5f7f410df7a8" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="17" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{3898acd8-9e76-4e3a-bd5c-f786070581b8}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="0f2f1471-5c80-47c6-b5fc-5f7f410df7a8">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d026c80c-8c89-4d76-b5a4-adafffa27ea9">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="0f2f1471-5c80-47c6-b5fc-5f7f410df7a8" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8DC9B193-5958-475E-B494-6373957BF4B4}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7CA334D1-571A-43A4-8A75-6DBF2F924EE5}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{339B8B26-57BD-4EC6-84FE-D37A6F4A38D5}"/>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{8c3d088b-6243-4963-a2e2-8b321ab7f8fc}" enabled="1" method="Standard" siteId="{d1323671-cdbe-4417-b4d4-bdb24b51316b}" removed="0"/>
